--- a/artfynd/A 2249-2026 artfynd.xlsx
+++ b/artfynd/A 2249-2026 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131046733</v>
+        <v>131046755</v>
       </c>
       <c r="B6" t="n">
-        <v>91809</v>
+        <v>57881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1124,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402493</v>
+        <v>402424</v>
       </c>
       <c r="R6" t="n">
-        <v>6818443</v>
+        <v>6818357</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131046755</v>
+        <v>131046733</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>91809</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,39 +1236,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>402424</v>
+        <v>402493</v>
       </c>
       <c r="R7" t="n">
-        <v>6818357</v>
+        <v>6818443</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131046711</v>
+        <v>131046844</v>
       </c>
       <c r="B9" t="n">
-        <v>83224</v>
+        <v>79244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>402363</v>
+        <v>402484</v>
       </c>
       <c r="R9" t="n">
-        <v>6818428</v>
+        <v>6818538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131046844</v>
+        <v>131046711</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>83224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>402484</v>
+        <v>402363</v>
       </c>
       <c r="R10" t="n">
-        <v>6818538</v>
+        <v>6818428</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 2249-2026 artfynd.xlsx
+++ b/artfynd/A 2249-2026 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131046755</v>
+        <v>131046733</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>91809</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,39 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402424</v>
+        <v>402493</v>
       </c>
       <c r="R6" t="n">
-        <v>6818357</v>
+        <v>6818443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131046733</v>
+        <v>131046755</v>
       </c>
       <c r="B7" t="n">
-        <v>91809</v>
+        <v>57881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,34 +1231,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>402493</v>
+        <v>402424</v>
       </c>
       <c r="R7" t="n">
-        <v>6818443</v>
+        <v>6818357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131046843</v>
+        <v>131046844</v>
       </c>
       <c r="B8" t="n">
         <v>79244</v>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402432</v>
+        <v>402484</v>
       </c>
       <c r="R8" t="n">
-        <v>6818480</v>
+        <v>6818538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131046844</v>
+        <v>131046711</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>83224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>402484</v>
+        <v>402363</v>
       </c>
       <c r="R9" t="n">
-        <v>6818538</v>
+        <v>6818428</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131046711</v>
+        <v>131046843</v>
       </c>
       <c r="B10" t="n">
-        <v>83224</v>
+        <v>79244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>402363</v>
+        <v>402432</v>
       </c>
       <c r="R10" t="n">
-        <v>6818428</v>
+        <v>6818480</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1989,30 +1989,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131046811</v>
+        <v>131046806</v>
       </c>
       <c r="B14" t="n">
-        <v>91829</v>
+        <v>83207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2020,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>402450</v>
+        <v>402340</v>
       </c>
       <c r="R14" t="n">
-        <v>6818298</v>
+        <v>6818363</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131046808</v>
+        <v>131046811</v>
       </c>
       <c r="B15" t="n">
         <v>91829</v>
@@ -2123,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>402323</v>
+        <v>402450</v>
       </c>
       <c r="R15" t="n">
-        <v>6818416</v>
+        <v>6818298</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2168,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,34 +2199,30 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131046806</v>
+        <v>131046808</v>
       </c>
       <c r="B16" t="n">
-        <v>83207</v>
+        <v>91829</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>402340</v>
+        <v>402323</v>
       </c>
       <c r="R16" t="n">
-        <v>6818363</v>
+        <v>6818416</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 2249-2026 artfynd.xlsx
+++ b/artfynd/A 2249-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131046732</v>
       </c>
       <c r="B2" t="n">
-        <v>92180</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131047025</v>
       </c>
       <c r="B3" t="n">
-        <v>89194</v>
+        <v>89195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131046847</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>131046733</v>
       </c>
       <c r="B6" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>131046844</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>131046711</v>
       </c>
       <c r="B9" t="n">
-        <v>83224</v>
+        <v>83225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>131046843</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,45 +1653,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131046763</v>
+        <v>131046735</v>
       </c>
       <c r="B11" t="n">
-        <v>92268</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402378</v>
+        <v>402448</v>
       </c>
       <c r="R11" t="n">
-        <v>6818392</v>
+        <v>6818295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,7 +1765,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131046735</v>
+        <v>131046788</v>
       </c>
       <c r="B12" t="n">
         <v>57884</v>
@@ -1791,7 +1796,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1800,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>402448</v>
+        <v>402473</v>
       </c>
       <c r="R12" t="n">
-        <v>6818295</v>
+        <v>6818425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1850,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,50 +1882,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046788</v>
+        <v>131046763</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>92269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>402473</v>
+        <v>402378</v>
       </c>
       <c r="R13" t="n">
-        <v>6818425</v>
+        <v>6818392</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,12 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,7 +1992,7 @@
         <v>131046806</v>
       </c>
       <c r="B14" t="n">
-        <v>83207</v>
+        <v>83208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>131046811</v>
       </c>
       <c r="B15" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>131046808</v>
       </c>
       <c r="B16" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>131046809</v>
       </c>
       <c r="B18" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>131046848</v>
       </c>
       <c r="B20" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>131046726</v>
       </c>
       <c r="B22" t="n">
-        <v>91772</v>
+        <v>91773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131046845</v>
+        <v>131047016</v>
       </c>
       <c r="B23" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,34 +2966,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>402575</v>
+        <v>402474</v>
       </c>
       <c r="R23" t="n">
-        <v>6818545</v>
+        <v>6818507</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3025,7 +3030,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3035,14 +3040,19 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -3062,10 +3072,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131047016</v>
+        <v>131046845</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3073,39 +3083,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>402474</v>
+        <v>402575</v>
       </c>
       <c r="R24" t="n">
-        <v>6818507</v>
+        <v>6818545</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3137,7 +3142,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3147,19 +3152,14 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>131046841</v>
       </c>
       <c r="B25" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 2249-2026 artfynd.xlsx
+++ b/artfynd/A 2249-2026 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131047025</v>
+        <v>131046847</v>
       </c>
       <c r="B3" t="n">
-        <v>89195</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402314</v>
+        <v>402380</v>
       </c>
       <c r="R3" t="n">
-        <v>6818423</v>
+        <v>6818405</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131046847</v>
+        <v>131047025</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>89195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402380</v>
+        <v>402314</v>
       </c>
       <c r="R4" t="n">
-        <v>6818405</v>
+        <v>6818423</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131046733</v>
+        <v>131046755</v>
       </c>
       <c r="B6" t="n">
-        <v>91810</v>
+        <v>57881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1124,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402493</v>
+        <v>402424</v>
       </c>
       <c r="R6" t="n">
-        <v>6818443</v>
+        <v>6818357</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131046755</v>
+        <v>131046733</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>91810</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,39 +1236,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>402424</v>
+        <v>402493</v>
       </c>
       <c r="R7" t="n">
-        <v>6818357</v>
+        <v>6818443</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131046844</v>
+        <v>131046711</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>83225</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402484</v>
+        <v>402363</v>
       </c>
       <c r="R8" t="n">
-        <v>6818538</v>
+        <v>6818428</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131046711</v>
+        <v>131046844</v>
       </c>
       <c r="B9" t="n">
-        <v>83225</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>402363</v>
+        <v>402484</v>
       </c>
       <c r="R9" t="n">
-        <v>6818428</v>
+        <v>6818538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 2249-2026 artfynd.xlsx
+++ b/artfynd/A 2249-2026 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131046847</v>
+        <v>131047025</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>89195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402380</v>
+        <v>402314</v>
       </c>
       <c r="R3" t="n">
-        <v>6818405</v>
+        <v>6818423</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131047025</v>
+        <v>131046847</v>
       </c>
       <c r="B4" t="n">
-        <v>89195</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402314</v>
+        <v>402380</v>
       </c>
       <c r="R4" t="n">
-        <v>6818423</v>
+        <v>6818405</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 2249-2026 artfynd.xlsx
+++ b/artfynd/A 2249-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131046732</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131047025</v>
       </c>
       <c r="B3" t="n">
-        <v>89195</v>
+        <v>89198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131046755</v>
+        <v>131046733</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>91813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,39 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402424</v>
+        <v>402493</v>
       </c>
       <c r="R6" t="n">
-        <v>6818357</v>
+        <v>6818443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131046733</v>
+        <v>131046755</v>
       </c>
       <c r="B7" t="n">
-        <v>91810</v>
+        <v>57881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,34 +1231,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>402493</v>
+        <v>402424</v>
       </c>
       <c r="R7" t="n">
-        <v>6818443</v>
+        <v>6818357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1885,7 +1885,7 @@
         <v>131046763</v>
       </c>
       <c r="B13" t="n">
-        <v>92269</v>
+        <v>92272</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,34 +1989,30 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131046806</v>
+        <v>131046811</v>
       </c>
       <c r="B14" t="n">
-        <v>83208</v>
+        <v>91833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2024,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>402340</v>
+        <v>402450</v>
       </c>
       <c r="R14" t="n">
-        <v>6818363</v>
+        <v>6818298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131046811</v>
+        <v>131046808</v>
       </c>
       <c r="B15" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>402450</v>
+        <v>402323</v>
       </c>
       <c r="R15" t="n">
-        <v>6818298</v>
+        <v>6818416</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2158,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2168,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,30 +2195,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131046808</v>
+        <v>131046806</v>
       </c>
       <c r="B16" t="n">
-        <v>91830</v>
+        <v>83208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>402323</v>
+        <v>402340</v>
       </c>
       <c r="R16" t="n">
-        <v>6818416</v>
+        <v>6818363</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2417,7 +2417,7 @@
         <v>131046809</v>
       </c>
       <c r="B18" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>131046726</v>
       </c>
       <c r="B22" t="n">
-        <v>91773</v>
+        <v>91776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131047016</v>
+        <v>131046845</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,39 +2966,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>402474</v>
+        <v>402575</v>
       </c>
       <c r="R23" t="n">
-        <v>6818507</v>
+        <v>6818545</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,7 +3025,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3040,19 +3035,14 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -3072,10 +3062,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131046845</v>
+        <v>131047016</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3083,34 +3073,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>402575</v>
+        <v>402474</v>
       </c>
       <c r="R24" t="n">
-        <v>6818545</v>
+        <v>6818507</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,7 +3137,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3152,14 +3147,19 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>

--- a/artfynd/A 2249-2026 artfynd.xlsx
+++ b/artfynd/A 2249-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131046732</v>
       </c>
       <c r="B2" t="n">
-        <v>92184</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131047025</v>
       </c>
       <c r="B3" t="n">
-        <v>89198</v>
+        <v>89199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131046847</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>131046733</v>
       </c>
       <c r="B6" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>131046711</v>
       </c>
       <c r="B8" t="n">
-        <v>83225</v>
+        <v>83226</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>131046844</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>131046843</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,50 +1653,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131046735</v>
+        <v>131046763</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>92273</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402448</v>
+        <v>402378</v>
       </c>
       <c r="R11" t="n">
-        <v>6818295</v>
+        <v>6818392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131046788</v>
+        <v>131046735</v>
       </c>
       <c r="B12" t="n">
         <v>57884</v>
@@ -1796,7 +1791,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1805,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>402473</v>
+        <v>402448</v>
       </c>
       <c r="R12" t="n">
-        <v>6818425</v>
+        <v>6818295</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1850,12 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,45 +1872,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046763</v>
+        <v>131046788</v>
       </c>
       <c r="B13" t="n">
-        <v>92272</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>402378</v>
+        <v>402473</v>
       </c>
       <c r="R13" t="n">
-        <v>6818392</v>
+        <v>6818425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1957,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,7 +1992,7 @@
         <v>131046811</v>
       </c>
       <c r="B14" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>131046808</v>
       </c>
       <c r="B15" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>131046806</v>
       </c>
       <c r="B16" t="n">
-        <v>83208</v>
+        <v>83209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>131046809</v>
       </c>
       <c r="B18" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>131046848</v>
       </c>
       <c r="B20" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>131046726</v>
       </c>
       <c r="B22" t="n">
-        <v>91776</v>
+        <v>91777</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>131046845</v>
       </c>
       <c r="B23" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>131046841</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 2249-2026 artfynd.xlsx
+++ b/artfynd/A 2249-2026 artfynd.xlsx
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131046711</v>
+        <v>131046844</v>
       </c>
       <c r="B8" t="n">
-        <v>83226</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402363</v>
+        <v>402484</v>
       </c>
       <c r="R8" t="n">
-        <v>6818428</v>
+        <v>6818538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131046844</v>
+        <v>131046843</v>
       </c>
       <c r="B9" t="n">
         <v>79246</v>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>402484</v>
+        <v>402432</v>
       </c>
       <c r="R9" t="n">
-        <v>6818538</v>
+        <v>6818480</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131046843</v>
+        <v>131046711</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>83226</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>402432</v>
+        <v>402363</v>
       </c>
       <c r="R10" t="n">
-        <v>6818480</v>
+        <v>6818428</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1989,30 +1989,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131046811</v>
+        <v>131046806</v>
       </c>
       <c r="B14" t="n">
-        <v>91834</v>
+        <v>83209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2020,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>402450</v>
+        <v>402340</v>
       </c>
       <c r="R14" t="n">
-        <v>6818298</v>
+        <v>6818363</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131046808</v>
+        <v>131046811</v>
       </c>
       <c r="B15" t="n">
         <v>91834</v>
@@ -2123,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>402323</v>
+        <v>402450</v>
       </c>
       <c r="R15" t="n">
-        <v>6818416</v>
+        <v>6818298</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2168,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,34 +2199,30 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131046806</v>
+        <v>131046808</v>
       </c>
       <c r="B16" t="n">
-        <v>83209</v>
+        <v>91834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>402340</v>
+        <v>402323</v>
       </c>
       <c r="R16" t="n">
-        <v>6818363</v>
+        <v>6818416</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 2249-2026 artfynd.xlsx
+++ b/artfynd/A 2249-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131046732</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131047025</v>
       </c>
       <c r="B3" t="n">
-        <v>89199</v>
+        <v>89201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131046847</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>131046753</v>
       </c>
       <c r="B5" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>131046733</v>
       </c>
       <c r="B6" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131046755</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131046844</v>
+        <v>131046711</v>
       </c>
       <c r="B8" t="n">
-        <v>79246</v>
+        <v>83228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402484</v>
+        <v>402363</v>
       </c>
       <c r="R8" t="n">
-        <v>6818538</v>
+        <v>6818428</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131046843</v>
+        <v>131046844</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>402432</v>
+        <v>402484</v>
       </c>
       <c r="R9" t="n">
-        <v>6818480</v>
+        <v>6818538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131046711</v>
+        <v>131046843</v>
       </c>
       <c r="B10" t="n">
-        <v>83226</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>402363</v>
+        <v>402432</v>
       </c>
       <c r="R10" t="n">
-        <v>6818428</v>
+        <v>6818480</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,45 +1653,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131046763</v>
+        <v>131046735</v>
       </c>
       <c r="B11" t="n">
-        <v>92273</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402378</v>
+        <v>402448</v>
       </c>
       <c r="R11" t="n">
-        <v>6818392</v>
+        <v>6818295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131046735</v>
+        <v>131046788</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1796,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1800,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>402448</v>
+        <v>402473</v>
       </c>
       <c r="R12" t="n">
-        <v>6818295</v>
+        <v>6818425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1850,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,50 +1882,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046788</v>
+        <v>131046763</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>92275</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>402473</v>
+        <v>402378</v>
       </c>
       <c r="R13" t="n">
-        <v>6818425</v>
+        <v>6818392</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,12 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,34 +1989,30 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131046806</v>
+        <v>131046811</v>
       </c>
       <c r="B14" t="n">
-        <v>83209</v>
+        <v>91836</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2024,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>402340</v>
+        <v>402450</v>
       </c>
       <c r="R14" t="n">
-        <v>6818363</v>
+        <v>6818298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131046811</v>
+        <v>131046808</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>402450</v>
+        <v>402323</v>
       </c>
       <c r="R15" t="n">
-        <v>6818298</v>
+        <v>6818416</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2158,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2168,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,30 +2195,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131046808</v>
+        <v>131046806</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>83211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>402323</v>
+        <v>402340</v>
       </c>
       <c r="R16" t="n">
-        <v>6818416</v>
+        <v>6818363</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,7 +2305,7 @@
         <v>131046740</v>
       </c>
       <c r="B17" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>131046809</v>
       </c>
       <c r="B18" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>131046754</v>
       </c>
       <c r="B19" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>131046848</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>131046752</v>
       </c>
       <c r="B21" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>131046726</v>
       </c>
       <c r="B22" t="n">
-        <v>91777</v>
+        <v>91779</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>131046845</v>
       </c>
       <c r="B23" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>131047016</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>131046841</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 2249-2026 artfynd.xlsx
+++ b/artfynd/A 2249-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131046732</v>
       </c>
       <c r="B2" t="n">
-        <v>92187</v>
+        <v>92188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131047025</v>
+        <v>131046847</v>
       </c>
       <c r="B3" t="n">
-        <v>89201</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402314</v>
+        <v>402380</v>
       </c>
       <c r="R3" t="n">
-        <v>6818423</v>
+        <v>6818405</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131046847</v>
+        <v>131047025</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>89202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402380</v>
+        <v>402314</v>
       </c>
       <c r="R4" t="n">
-        <v>6818405</v>
+        <v>6818423</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
         <v>131046753</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>131046733</v>
       </c>
       <c r="B6" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131046755</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>131046711</v>
       </c>
       <c r="B8" t="n">
-        <v>83228</v>
+        <v>83229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>131046844</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>131046843</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,50 +1653,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131046735</v>
+        <v>131046763</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>92276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402448</v>
+        <v>402378</v>
       </c>
       <c r="R11" t="n">
-        <v>6818295</v>
+        <v>6818392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131046788</v>
+        <v>131046735</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1791,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1805,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>402473</v>
+        <v>402448</v>
       </c>
       <c r="R12" t="n">
-        <v>6818425</v>
+        <v>6818295</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1850,12 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,45 +1872,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046763</v>
+        <v>131046788</v>
       </c>
       <c r="B13" t="n">
-        <v>92275</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>402378</v>
+        <v>402473</v>
       </c>
       <c r="R13" t="n">
-        <v>6818392</v>
+        <v>6818425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1957,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,30 +1989,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131046811</v>
+        <v>131046806</v>
       </c>
       <c r="B14" t="n">
-        <v>91836</v>
+        <v>83212</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2020,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>402450</v>
+        <v>402340</v>
       </c>
       <c r="R14" t="n">
-        <v>6818298</v>
+        <v>6818363</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131046808</v>
+        <v>131046811</v>
       </c>
       <c r="B15" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>402323</v>
+        <v>402450</v>
       </c>
       <c r="R15" t="n">
-        <v>6818416</v>
+        <v>6818298</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2168,7 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,34 +2199,30 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131046806</v>
+        <v>131046808</v>
       </c>
       <c r="B16" t="n">
-        <v>83211</v>
+        <v>91837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>402340</v>
+        <v>402323</v>
       </c>
       <c r="R16" t="n">
-        <v>6818363</v>
+        <v>6818416</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,7 +2305,7 @@
         <v>131046740</v>
       </c>
       <c r="B17" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>131046809</v>
       </c>
       <c r="B18" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>131046754</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>131046848</v>
       </c>
       <c r="B20" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>131046752</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>131046726</v>
       </c>
       <c r="B22" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131046845</v>
+        <v>131047016</v>
       </c>
       <c r="B23" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,34 +2966,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>402575</v>
+        <v>402474</v>
       </c>
       <c r="R23" t="n">
-        <v>6818545</v>
+        <v>6818507</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3025,7 +3030,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3035,14 +3040,19 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -3062,10 +3072,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131047016</v>
+        <v>131046845</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3073,39 +3083,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>402474</v>
+        <v>402575</v>
       </c>
       <c r="R24" t="n">
-        <v>6818507</v>
+        <v>6818545</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3137,7 +3142,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3147,19 +3152,14 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>131046841</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 2249-2026 artfynd.xlsx
+++ b/artfynd/A 2249-2026 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131046847</v>
+        <v>131047025</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>89202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402380</v>
+        <v>402314</v>
       </c>
       <c r="R3" t="n">
-        <v>6818405</v>
+        <v>6818423</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131047025</v>
+        <v>131046847</v>
       </c>
       <c r="B4" t="n">
-        <v>89202</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402314</v>
+        <v>402380</v>
       </c>
       <c r="R4" t="n">
-        <v>6818423</v>
+        <v>6818405</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1653,45 +1653,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131046763</v>
+        <v>131046735</v>
       </c>
       <c r="B11" t="n">
-        <v>92276</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402378</v>
+        <v>402448</v>
       </c>
       <c r="R11" t="n">
-        <v>6818392</v>
+        <v>6818295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,7 +1765,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131046735</v>
+        <v>131046788</v>
       </c>
       <c r="B12" t="n">
         <v>57887</v>
@@ -1791,7 +1796,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1800,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>402448</v>
+        <v>402473</v>
       </c>
       <c r="R12" t="n">
-        <v>6818295</v>
+        <v>6818425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1850,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,50 +1882,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046788</v>
+        <v>131046763</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>92276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>402473</v>
+        <v>402378</v>
       </c>
       <c r="R13" t="n">
-        <v>6818425</v>
+        <v>6818392</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,12 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2955,10 +2955,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131047016</v>
+        <v>131046845</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,39 +2966,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>402474</v>
+        <v>402575</v>
       </c>
       <c r="R23" t="n">
-        <v>6818507</v>
+        <v>6818545</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,7 +3025,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3040,19 +3035,14 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -3072,10 +3062,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131046845</v>
+        <v>131047016</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3083,34 +3073,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>402575</v>
+        <v>402474</v>
       </c>
       <c r="R24" t="n">
-        <v>6818545</v>
+        <v>6818507</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,7 +3137,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3152,14 +3147,19 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>

--- a/artfynd/A 2249-2026 artfynd.xlsx
+++ b/artfynd/A 2249-2026 artfynd.xlsx
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131046711</v>
+        <v>131046843</v>
       </c>
       <c r="B8" t="n">
-        <v>83229</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402363</v>
+        <v>402432</v>
       </c>
       <c r="R8" t="n">
-        <v>6818428</v>
+        <v>6818480</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131046844</v>
+        <v>131046711</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>83229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>402484</v>
+        <v>402363</v>
       </c>
       <c r="R9" t="n">
-        <v>6818538</v>
+        <v>6818428</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131046843</v>
+        <v>131046844</v>
       </c>
       <c r="B10" t="n">
         <v>79249</v>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>402432</v>
+        <v>402484</v>
       </c>
       <c r="R10" t="n">
-        <v>6818480</v>
+        <v>6818538</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,50 +1653,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131046735</v>
+        <v>131046763</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>92276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402448</v>
+        <v>402378</v>
       </c>
       <c r="R11" t="n">
-        <v>6818295</v>
+        <v>6818392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,45 +1877,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131046763</v>
+        <v>131046735</v>
       </c>
       <c r="B13" t="n">
-        <v>92276</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>402378</v>
+        <v>402448</v>
       </c>
       <c r="R13" t="n">
-        <v>6818392</v>
+        <v>6818295</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,34 +1989,30 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131046806</v>
+        <v>131046811</v>
       </c>
       <c r="B14" t="n">
-        <v>83212</v>
+        <v>91837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2024,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>402340</v>
+        <v>402450</v>
       </c>
       <c r="R14" t="n">
-        <v>6818363</v>
+        <v>6818298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,7 +2092,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131046811</v>
+        <v>131046808</v>
       </c>
       <c r="B15" t="n">
         <v>91837</v>
@@ -2127,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>402450</v>
+        <v>402323</v>
       </c>
       <c r="R15" t="n">
-        <v>6818298</v>
+        <v>6818416</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2158,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2168,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,30 +2195,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131046808</v>
+        <v>131046806</v>
       </c>
       <c r="B16" t="n">
-        <v>91837</v>
+        <v>83212</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>402323</v>
+        <v>402340</v>
       </c>
       <c r="R16" t="n">
-        <v>6818416</v>
+        <v>6818363</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
